--- a/Stats Sheet/Round Gaps/World Cup.xlsx
+++ b/Stats Sheet/Round Gaps/World Cup.xlsx
@@ -325,12 +325,12 @@
     <x:t>Jordtim</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>LegoBeast</x:t>
   </x:si>
   <x:si>
+    <x:t>Nikikula</x:t>
+  </x:si>
+  <x:si>
     <x:t>ScottPirie</x:t>
   </x:si>
   <x:si>
@@ -685,7 +685,7 @@
     <x:t>TheKevGuy</x:t>
   </x:si>
   <x:si>
-    <x:t>tonylmao</x:t>
+    <x:t>Tonylmao</x:t>
   </x:si>
   <x:si>
     <x:t>zCent</x:t>
@@ -2731,18 +2731,9 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D80" s="0">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H80" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I80" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J80" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K80" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -2757,9 +2748,18 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D81" s="0">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H81" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J81" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K81" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
